--- a/public/share/data/伤病与体测.xlsx
+++ b/public/share/data/伤病与体测.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1844,6 +1844,397 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>7/7首报小腿酸痛→7/8首发90′→7/9臀+小腿→7/12正常训练RPE4→7/13晨间正常✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>脚掌(跖骨区)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>过劳性·持续监控(如持续建议影像检查)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>脚踝</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>不适·已恢复✅</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1天</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>全身(发烧→肠胃不适)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>其他/疾病·已恢复✅</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>非训练</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>部分2天</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>脚踝</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>疼痛·待评估(7/19门将出战风险)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>腘绳肌</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>肌肉紧张·监控中(拉伤前兆信号)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>晨间自评</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>左大腿后群(腘绳肌)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>肌肉紧张·监控中(拉伤前兆信号)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>晨间自评</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>内踝</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>不适·监控中</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>晨间自评</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>腘绳肌</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>肌肉紧张·已恢复✅</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>晨间自评</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1天</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>

--- a/public/share/data/伤病与体测.xlsx
+++ b/public/share/data/伤病与体测.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -178,6 +178,10 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -373,7 +377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -479,6 +483,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -627,10 +645,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1081,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1209,9 +1233,18 @@
           <t>接触</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>~35天</t>
+        </is>
+      </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>MCL内侧副韧带撕裂 | 等级待确认 | 7/7未填RPE/睡眠/酸痛</t>
+          <t>MCL内侧副韧带撕裂 | 等级待确认 | 7/7未填RPE/睡眠/酸痛
+── 7/21归队 ──
+跑步机直线15km/h✅ | 变速/变向/急停/启动受限
+MCL伤后第5周，两周窗口回归合练
+等级待确认(I/II级可能性大，4周初步愈合)</t>
         </is>
       </c>
     </row>
@@ -2235,6 +2268,593 @@
       <c r="J24" t="inlineStr">
         <is>
           <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>脚腕(踝)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>疼痛·🆕新信号·待观察</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>力量房训练</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>7/22力量房后报告脚腕疼·非对抗·可能过劳·建议连续监控·如持续建议影像</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>全身/睡眠</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>睡眠严重不足·疲劳管理⚠️</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>7/22晨间睡眠=5(全队最差)·原因待查·今日降量·连续监控睡眠</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>内踝</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>不适·已恢复✅</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>晨间自评</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>7/17首报→7/18仍有→7/22训练正常·已恢复·关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>膝关节MCL</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>韧带撕裂·归队D2·康复进展中</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>接触</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>~37天</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>7/21归队→7/22完成上午力量房(上肢正常+下肢自重)+下午场地单独训练·RPE=3/3·进展顺利✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>脚踝</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>疼痛·持续管理·D9·7/19扛满全场→7/22力量房全跟</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>7天+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>脚踝痛D9·力量房全跟(康复方案)+下午场地RPE=6·继续踝泵+冰敷·功能在恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>左大腿后群(腘绳肌)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>肌肉紧张·持续监控·改善中</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>晨间自评</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>6天+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>7/17首报→7/19 RPE=10→7/22力量房(臀桥代深蹲·不硬拉)+场地RPE=5·后群仍紧但可控</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>左膝关节</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>髌腱炎·酸痛突增⚠️(1→4)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>训练(三球门11v11)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>非接触/过劳</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7/23场地训练后左膝酸痛从7/22的1→突增至4·RPE=7·可能因7/22力量房(保蹲30kg+腿屈伸80kg)+今日三球门大覆盖面积叠加·明日评估离心训练量·如持续建议减量至等长阶段</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>脚腕+全身肌肉</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>过劳性·肌肉酸痛·脚腕疼持续监控</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>训练(连续两日)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>非接触/过劳</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7/22力量房后脚腕疼→7/23场地后报告肌肉酸·7/19跑10km⚡+7/22全量力量+7/23三球门对抗→累积负荷过大·建议D-2降量·如脚腕持续疼建议影像</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>肩膀</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>不适·轻微·待观察</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7/23晨间报告肩膀疼·门将位置可能因扑救/头球游戏反复起跳引起·程度轻微·继续观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>全身/神经肌肉</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>过劳性·累积疲劳预警⚠️⚠️⚠️</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>训练(连续多日高负荷)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>非接触/过劳</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>7/19跑10km⚡→7/22全量力量房(RPE=6)→7/23三球门11v11(RPE=8全队最高)·三天累积负荷超标·D-3/D-2必须降量·如7/24 RPE仍≥7建议7/26替补·软组织放松优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>全身/睡眠</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>睡眠恶化+投入度异常⚠️</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>训练(4v4)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>非接触</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7/22睡2→7/23睡4(恶化)·RPE从6骤降至2·4v4投入度待观察·可能因新人适应期身心疲劳·建议沟通了解原因</t>
         </is>
       </c>
     </row>

--- a/public/share/data/伤病与体测.xlsx
+++ b/public/share/data/伤病与体测.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3266,19 +3266,103 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>左腿后群</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>🆕轻度反应·D+2恢复课后报告</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>训练后</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>D+2恢复课(60'慢跑+游戏)后报告左腿后群有点反应·无急性损伤·D+3观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>脚腕微痛</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>🆕轻度·继续训练</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>晨间</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>8/11晨间报告脚腕微痛·仍参加D+2恢复课RPE=2·观察</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="C35:E35"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="C32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/伤病与体测.xlsx
+++ b/public/share/data/伤病与体测.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3347,6 +3347,334 @@
       <c r="K67" t="inlineStr">
         <is>
           <t>8/11晨间报告脚腕微痛·仍参加D+2恢复课RPE=2·观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>左腿后群反应</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>✅已恢复</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>8/11首报→8/12正常✅·仅持续1天</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>脚腕微痛</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>✅已恢复</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>8/11首报→8/12正常✅·仅持续1天</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>内收肌紧</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>🟡持续·MD-3 RPE=5·MD-2减量观察</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>8/11首报→8/12仍有点紧·MD-3 RPE=5正常训练·MD-2减量+客场出行注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>脚踝疼</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>🟡D6·持续但可控·RPE=2</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>8/7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>8/7脚崴→持续脚踝疼·已6天·MD-3低负荷RPE=2·赛前评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>左膝髌腱炎</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>🟡持续·MD-3 RPE=3·受控</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>左膝持续·MD-3 RPE=3限负荷·离心动作受控·赛前等长策略维持</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>脚崴</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>🔴D7·8/13缺席训练</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>8/7</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>8/7脚崴→持续·8/13未参加训练·8/15客场青岛前需评估能否出战</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>黄牌停赛</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>🟡停赛·8/15青岛不上场</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>黄牌停赛·8/13未参加战术演练改为单练·8/15客场青岛不能出场·未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>脚微痛</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>🟡轻度·晨间报告</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>8/13晨间报告脚微痛·仍参训RPE=3·8/15客场青岛前观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>左后群紧</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>🟡晨间报告·睡眠4偏高</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>8/13晨间报告左后群紧·睡眠4·RPE=3参训·MCL史需关注·8/15赛前评估</t>
         </is>
       </c>
     </row>

--- a/public/share/data/伤病与体测.xlsx
+++ b/public/share/data/伤病与体测.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3678,19 +3678,130 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>🟡复发·8/13正常→8/14又疼</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>8/13晨间正常→8/14晨间腰疼·8/15赛前观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>略不舒服</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>🟡晨间报告·睡3疲3</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>8/14晨间略不舒服·睡3疲3·RPE=6踩场·赛前评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>🟡D8·酸痛已降至1·RPE=5参训</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>8/7</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>脚踝D8·8/14酸痛1(好转)·踩场RPE=5·8/15能否出战待评估</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="C32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/伤病与体测.xlsx
+++ b/public/share/data/伤病与体测.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3789,16 +3789,184 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>🟡D9·首发打满90min RPE=8·坚持出战</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>8/7</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>8/7脚崴→8/15客场青岛首发打满90min RPE=8·脚踝仍痛但扛满全场·赛前评估后坚持出战·赛后冰敷踝泵</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>右膝MCL撕裂</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>✅里程碑·63'替补登场27min RPE=7·正式比赛首秀</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>接触</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>6月MCL撕裂→康复近2个月→8/15客vs青岛红狮63′替补登场27min·正式比赛首秀·RPE=7·MCL恢复至可比赛水平·赛后观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>✅已恢复</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>8/14晨间腰疼复发→8/15晨间正常·替补未登场(热身15min RPE=3)·关闭✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>略不舒服</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>✅已恢复·首发90min RPE=10</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>8/14晨间略不舒服→8/15晨间正常(睡1疲1酸1)·客场首发打满90min RPE=10·状态恢复✅</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A28:K28"/>
     <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="A1:K1"/>

--- a/public/share/data/伤病与体测.xlsx
+++ b/public/share/data/伤病与体测.xlsx
@@ -1265,6 +1265,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1656,6 +1657,8 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
@@ -2307,6 +2310,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28"/>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
@@ -2871,6 +2875,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -2918,6 +2923,7 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -2957,6 +2963,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
@@ -2994,6 +3001,7 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -3558,7 +3566,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>🔴D7·8/13缺席训练</t>
+          <t>🟡D7·参训RPE=3·脚踝疼·赛前评估</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3568,7 +3576,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/7脚崴→持续·8/13未参加训练·8/15客场青岛前需评估能否出战</t>
+          <t>8/7脚崴→持续·8/13参训RPE=3(脚踝疼)·8/14踩场·8/15客场青岛前需评估能否出战</t>
         </is>
       </c>
     </row>
@@ -3963,13 +3971,13 @@
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="C35:E35"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="C32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
